--- a/data/seed/portfolio/L-2025-3948/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-3948/vypiska_2026-07_09.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I193"/>
+  <dimension ref="A1:I157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -560,38 +560,38 @@
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n">
-        <v>133388000</v>
+        <v>65294000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yulduz Poligraf XK</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>266699741</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000250503521001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №163/26 от 01.07.2026</t>
+          <t>Оплата по счет-фактуре №4676 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>02.07.2026</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -599,40 +599,40 @@
           <t>101</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n">
-        <v>40082000</v>
-      </c>
+      <c r="C11" s="2" t="n">
+        <v>33045000</v>
+      </c>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Buxoro Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>225137817</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000179102777001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4540 за поставленный товар</t>
+          <t>Оплата за сырье по договору №43/26 от 01.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>02.07.2026</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -640,33 +640,33 @@
           <t>102</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n">
-        <v>27162000</v>
-      </c>
+      <c r="C12" s="2" t="n">
+        <v>175876000</v>
+      </c>
+      <c r="D12" s="2" t="n"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chust Agro MChJ</t>
+          <t>Buxoro Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>262401919</t>
+          <t>225137817</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000060416519001</t>
+          <t>20208000179102777001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №26/26, QQS 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №1222</t>
         </is>
       </c>
     </row>
@@ -683,38 +683,38 @@
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>61226000</v>
+        <v>157667000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jizzax Plastik AJ</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>261879358</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000005154280001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6695 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №4609 от 03.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -724,31 +724,31 @@
       </c>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n">
-        <v>58572000</v>
+        <v>105235000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chust Agro MChJ</t>
+          <t>Toshkent Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>262401919</t>
+          <t>240191920</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000060416519001</t>
+          <t>20208000041651902001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №244/26 от 03.07.2026</t>
+          <t>ОПЛАТА ПО С/Ф №6880 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
     </row>
@@ -765,21 +765,21 @@
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
-        <v>74169000</v>
+        <v>95389000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nurafshon Non MChJ</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>336469147</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000994650823001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №4/26 от 06.07.2026</t>
+          <t>Предоплата за товар по дог. №182/26 от 06.07.2026</t>
         </is>
       </c>
     </row>
@@ -806,31 +806,31 @@
       </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n">
-        <v>39582000</v>
+        <v>54399000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Toshkent Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>240191920</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000041651902001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Оплата за продукцю по дог. №56/26, НДС 12%</t>
+          <t>Shartnoma №86/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
@@ -845,33 +845,33 @@
           <t>107</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n">
-        <v>32203000</v>
-      </c>
+      <c r="C17" s="2" t="n">
+        <v>37060000</v>
+      </c>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Buxoro Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>225137817</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000179102777001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №94/26, НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №4925</t>
         </is>
       </c>
     </row>
@@ -886,33 +886,33 @@
           <t>108</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n">
-        <v>19862000</v>
-      </c>
+      <c r="C18" s="2" t="n">
+        <v>67273000</v>
+      </c>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nurafshon Non MChJ</t>
+          <t>Navoiy Poligraf XK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>336469147</t>
+          <t>309846072</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000994650823001</t>
+          <t>20208000186649829001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3068 от 06.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товары согласно с/ф №4596</t>
         </is>
       </c>
     </row>
@@ -927,33 +927,28 @@
           <t>109</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n">
-        <v>13699000</v>
-      </c>
+      <c r="C19" s="2" t="n">
+        <v>222400000</v>
+      </c>
+      <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>305246474</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №224/26 от 06.07.2026</t>
+          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
     </row>
@@ -969,27 +964,32 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>222400000</v>
+        <v>459006000</v>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Oltin Vodiy Mato MChJ</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>258917044</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000513855120001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Xom ashyo uchun to'lov, shartn. №120/26, QQS bilan</t>
         </is>
       </c>
     </row>
@@ -1010,34 +1010,34 @@
       <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Navro'z Qurilish Materiallari MChJ</t>
+          <t>Bahor Qurilish Materiallari AJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>254190271</t>
+          <t>230192105</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000548897054001</t>
+          <t>20208000971885157001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Аренда помещения за июль, дог. №32/25</t>
+          <t>АРЕНДА ПОМЕЩЕНИЯ ЗА ИЮЛЬ, ДОГ. №12/21</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1045,23 +1045,23 @@
           <t>112</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n">
-        <v>24966000</v>
-      </c>
+      <c r="C22" s="2" t="n">
+        <v>41016000</v>
+      </c>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jizzax Plastik AJ</t>
+          <t>Oltin Vodiy Mato MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>261879358</t>
+          <t>258917044</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000005154280001</t>
+          <t>20208000513855120001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1071,14 +1071,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №207/26, НДС 12%</t>
+          <t>Предоплата за материалы по договору №128/26</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1088,38 +1088,38 @@
       </c>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n">
-        <v>15925000</v>
+        <v>250785000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Jizzax Plastik AJ</t>
+          <t>Toshkent Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>261879358</t>
+          <t>240191920</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000005154280001</t>
+          <t>20208000041651902001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1920 за поставленный товар</t>
+          <t>Оплата по с/ф №4036 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1129,38 +1129,38 @@
       </c>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n">
-        <v>13871000</v>
+        <v>240162000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №206/26 от 08.07.2026</t>
+          <t>Оплата за продукцию по договору №148/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1168,40 +1168,40 @@
           <t>115</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>77248000</v>
-      </c>
-      <c r="D25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n">
+        <v>221391000</v>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Toshkent Avto Savdo MChJ</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>200251378</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000751791027001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №96/26</t>
+          <t>Оплата за товар по с/ф №2370 от 10.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1211,31 +1211,31 @@
       </c>
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n">
-        <v>20586000</v>
+        <v>73750000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Qo'qon Plastik MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>287935800</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000515428065001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3140 от 09.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №5604 от 10.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1250,40 +1250,40 @@
           <t>117</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n">
-        <v>97386000</v>
-      </c>
+      <c r="C27" s="2" t="n">
+        <v>51796000</v>
+      </c>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Navoiy Poligraf XK</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>309846072</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000186649829001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №123/26, НДС 12%</t>
+          <t>Оплата за транспортные услуги по дог. №28/26</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1291,40 +1291,40 @@
           <t>118</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n">
-        <v>54130000</v>
-      </c>
+      <c r="C28" s="2" t="n">
+        <v>1006121000</v>
+      </c>
+      <c r="D28" s="2" t="n"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Yulduz Plastik MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>229970515</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000350579471001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2758</t>
+          <t>Предоплата за материалы по договору №114/26</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1332,40 +1332,40 @@
           <t>119</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n">
-        <v>24587000</v>
-      </c>
+      <c r="C29" s="2" t="n">
+        <v>30327000</v>
+      </c>
+      <c r="D29" s="2" t="n"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Plastik MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>290662356</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000062492032001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5888 10.07.2026, QQS bilan</t>
+          <t>Уплата социального налога за июнь</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1374,39 +1374,39 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>96585000</v>
+        <v>30327000</v>
       </c>
       <c r="D30" s="2" t="n"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nukus Dori-Darmon XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>277098460</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000251866498001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №49/26</t>
+          <t>НДФЛ за июнь 2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1414,40 +1414,40 @@
           <t>121</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n">
-        <v>111631000</v>
-      </c>
-      <c r="D31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n">
+        <v>268451000</v>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Savdo MChJ</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>240589170</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000415138551001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №4305</t>
+          <t>Оплата за товар по счет-фактуре №973 от 15.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1456,39 +1456,34 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>147147000</v>
+        <v>152400000</v>
       </c>
       <c r="D32" s="2" t="n"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nukus Dori-Darmon XK</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>277098460</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-3948)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000251866498001</t>
+          <t>16307000251586252417</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №53/26</t>
+          <t>Kredit shartnomasi L-2025-3948 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1498,38 +1493,38 @@
       </c>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n">
-        <v>355873000</v>
+        <v>54552000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Farg'ona Sut Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>273042818</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000838886010001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1244 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №55/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1537,23 +1532,23 @@
           <t>124</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n">
-        <v>64038000</v>
-      </c>
+      <c r="C34" s="2" t="n">
+        <v>38374000</v>
+      </c>
+      <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Yulduz Moy MChJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>392350013</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000942890894001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1563,14 +1558,14 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Shartnoma №54/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за материалы по договору №193/26</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1580,38 +1575,38 @@
       </c>
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="n">
-        <v>38650000</v>
+        <v>1042204000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Omad Tekstil MChJ</t>
+          <t>Bog'ishamol Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>382730428</t>
+          <t>346914789</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000878388860001</t>
+          <t>20208000465082397001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №326</t>
+          <t>Оплата за продукцию по дог. №135/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1620,39 +1615,39 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>51674000</v>
+        <v>23644000</v>
       </c>
       <c r="D36" s="2" t="n"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Toshkent Avto Savdo MChJ</t>
+          <t>Navoiy Poligraf XK</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>200251378</t>
+          <t>309846072</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000751791027001</t>
+          <t>20208000186649829001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №273/26 от 13.07.2026, НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №106/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1661,39 +1656,39 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>361907000</v>
+        <v>143678000</v>
       </c>
       <c r="D37" s="2" t="n"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Yangi Hayot Dori-Darmon MChJ</t>
+          <t>Buxoro Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>372599213</t>
+          <t>225137817</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000876079668001</t>
+          <t>20208000179102777001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №8827</t>
+          <t>Оплата за сырье по договору №138/26 от 20.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1701,40 +1696,40 @@
           <t>128</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n">
-        <v>86584000</v>
-      </c>
+      <c r="C38" s="2" t="n">
+        <v>25892000</v>
+      </c>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Buxoro Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>225137817</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000179102777001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №207/26, НДС 12%</t>
+          <t>Tovarlar uchun to'lov h/f №4180</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1742,40 +1737,40 @@
           <t>129</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n">
-        <v>18578000</v>
-      </c>
+      <c r="C39" s="2" t="n">
+        <v>40124000</v>
+      </c>
+      <c r="D39" s="2" t="n"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Chust Agro MChJ</t>
+          <t>Buxoro Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>262401919</t>
+          <t>225137817</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000060416519001</t>
+          <t>20208000179102777001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №181/26, QQS 12%</t>
+          <t>Предоплата за материалы по договору №122/26</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1783,35 +1778,40 @@
           <t>130</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n">
-        <v>152400000</v>
-      </c>
-      <c r="D40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n">
+        <v>544544000</v>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-3948)</t>
+          <t>Navro'z Polimer MChJ</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>16307000251586252417</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-3948 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Предоплата за товар по договору №13/26 от 22.07.2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1819,40 +1819,40 @@
           <t>131</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n">
-        <v>30327000</v>
-      </c>
-      <c r="D41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n">
+        <v>70481000</v>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Уплата социального налога за июнь</t>
+          <t>Оплата по счет-фактуре №2172 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>30327000</v>
+        <v>40069000</v>
       </c>
       <c r="D42" s="2" t="n"/>
       <c r="E42" t="inlineStr">
@@ -1886,14 +1886,14 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
+          <t>НДС за июнь 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1903,21 +1903,21 @@
       </c>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n">
-        <v>45214000</v>
+        <v>94820000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nurafshon Non MChJ</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>336469147</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000994650823001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -1927,14 +1927,14 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №85/26, НДС 12%</t>
+          <t>Оплата за продукцию по дог. №277/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1942,23 +1942,23 @@
           <t>134</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n">
-        <v>160529000</v>
-      </c>
+      <c r="C44" s="2" t="n">
+        <v>15244000</v>
+      </c>
+      <c r="D44" s="2" t="n"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000227154788001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1968,14 +1968,14 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дг. №254/26 от 20.07.2026</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1983,40 +1983,40 @@
           <t>135</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n">
-        <v>122941000</v>
-      </c>
+      <c r="C45" s="2" t="n">
+        <v>48828000</v>
+      </c>
+      <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Chust Agro MChJ</t>
+          <t>Buxoro Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>262401919</t>
+          <t>225137817</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000060416519001</t>
+          <t>20208000179102777001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №224/26 от 20.07.2026</t>
+          <t>Оплата за упаковочные материалы, с/ф №4043</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2024,40 +2024,40 @@
           <t>136</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n">
-        <v>74798000</v>
-      </c>
+      <c r="C46" s="2" t="n">
+        <v>62311000</v>
+      </c>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Navoiy Poligraf XK</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>309846072</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000186649829001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7578 от 20.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за сырье по дог. №155/26 от 27.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2065,23 +2065,23 @@
           <t>137</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n">
-        <v>37152000</v>
-      </c>
+      <c r="C47" s="2" t="n">
+        <v>233633000</v>
+      </c>
+      <c r="D47" s="2" t="n"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Yulduz Moy MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>392350013</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000942890894001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2091,14 +2091,14 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7407 от 20.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №35/26</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2106,40 +2106,40 @@
           <t>138</t>
         </is>
       </c>
-      <c r="C48" s="2" t="n"/>
-      <c r="D48" s="2" t="n">
-        <v>37069000</v>
-      </c>
+      <c r="C48" s="2" t="n">
+        <v>290366000</v>
+      </c>
+      <c r="D48" s="2" t="n"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Shodlik Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>290271954</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000897054744001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4812 от 20.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за транспортные услуги по дог. №121/26</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2147,40 +2147,40 @@
           <t>139</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n">
-        <v>27369000</v>
-      </c>
+      <c r="C49" s="2" t="n">
+        <v>118187000</v>
+      </c>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Jizzax Plastik AJ</t>
+          <t>Buxoro Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>261879358</t>
+          <t>225137817</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000005154280001</t>
+          <t>20208000179102777001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №13/26 от 20.07.2026</t>
+          <t>Tovarlar uchun to'lov h/f №9164</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2188,40 +2188,35 @@
           <t>140</t>
         </is>
       </c>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n">
-        <v>15399000</v>
-      </c>
+      <c r="C50" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Chust Agro MChJ</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>262401919</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000060416519001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №833 от 20.07.2026, в т.ч. НДС 12%</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за июль</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2229,40 +2224,40 @@
           <t>141</t>
         </is>
       </c>
-      <c r="C51" s="2" t="n">
-        <v>42990000</v>
-      </c>
-      <c r="D51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n">
+        <v>151238000</v>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Toshkent Avto Savdo MChJ</t>
+          <t>Toshkent Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>200251378</t>
+          <t>240191920</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000751791027001</t>
+          <t>20208000041651902001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №219/26</t>
+          <t>Оплата за товар по счет-фактуре №4050 от 03.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2270,40 +2265,40 @@
           <t>142</t>
         </is>
       </c>
-      <c r="C52" s="2" t="n">
-        <v>106494000</v>
-      </c>
-      <c r="D52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n">
+        <v>95096000</v>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Toshkent Avto Savdo MChJ</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>200251378</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000751791027001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №236/26</t>
+          <t>Оплата по счет-фактуре №2405 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2312,39 +2307,39 @@
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>438177000</v>
+        <v>70585000</v>
       </c>
       <c r="D53" s="2" t="n"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Toshkent Avto Savdo MChJ</t>
+          <t>Buxoro Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>200251378</t>
+          <t>225137817</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000751791027001</t>
+          <t>20208000179102777001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №111/26, QQS bilan</t>
+          <t>Xom ashyo uchun to'lov, shartn. №17/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2352,40 +2347,40 @@
           <t>144</t>
         </is>
       </c>
-      <c r="C54" s="2" t="n">
-        <v>478450000</v>
-      </c>
-      <c r="D54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n">
+        <v>25699000</v>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Toshkent Avto Savdo MChJ</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>200251378</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000751791027001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №97/26</t>
+          <t>Оплата по счет-фактуре №4958 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2395,38 +2390,38 @@
       </c>
       <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="n">
-        <v>1008142000</v>
+        <v>36676000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Angren Oziq-ovqat Savdo MChJ</t>
+          <t>Bog'ishamol Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>380225346</t>
+          <t>346914789</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000345687817001</t>
+          <t>20208000465082397001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №7674 от 21.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №1844 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2436,21 +2431,21 @@
       </c>
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n">
-        <v>14807000</v>
+        <v>32741000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Jizzax Plastik AJ</t>
+          <t>Marg'ilon Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>261879358</t>
+          <t>223624727</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000005154280001</t>
+          <t>20208000373641798001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2460,14 +2455,14 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Shartnoma №124/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartn. №210/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2476,39 +2471,34 @@
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>40425000</v>
+        <v>225995000</v>
       </c>
       <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>QQS iyun 2026 uchun</t>
+          <t>Заработная плата за июль 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2518,38 +2508,38 @@
       </c>
       <c r="C58" s="2" t="n"/>
       <c r="D58" s="2" t="n">
-        <v>24354000</v>
+        <v>203268000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №99/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №179/26 от 06.08.2026</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2557,40 +2547,40 @@
           <t>149</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n">
-        <v>150520000</v>
-      </c>
-      <c r="D59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n">
+        <v>23534000</v>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Toshkent Avto Savdo MChJ</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>200251378</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000751791027001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №177/26</t>
+          <t>Предоплата за товар по дог. №157/26 от 06.08.2026</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2599,39 +2589,39 @@
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>160316000</v>
+        <v>136958000</v>
       </c>
       <c r="D60" s="2" t="n"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Toshkent Avto Savdo MChJ</t>
+          <t>Yulduz Moy MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>200251378</t>
+          <t>392350013</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000751791027001</t>
+          <t>20208000942890894001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №141/26 от 23.07.2026, НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №2436</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2639,23 +2629,23 @@
           <t>151</t>
         </is>
       </c>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n">
-        <v>333567000</v>
-      </c>
+      <c r="C61" s="2" t="n">
+        <v>24784000</v>
+      </c>
+      <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Plastik MChJ</t>
+          <t>Bahor Qurilish Materiallari AJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>290662356</t>
+          <t>230192105</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000062492032001</t>
+          <t>20208000971885157001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2665,14 +2655,14 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №6910 27.07.2026, QQS BILAN</t>
+          <t>АРЕНДА ПОМЕЩЕНИЯ ЗА АВГУСТ, ДОГ. №12/21</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2680,23 +2670,23 @@
           <t>152</t>
         </is>
       </c>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="n">
-        <v>26463000</v>
-      </c>
+      <c r="C62" s="2" t="n">
+        <v>602848000</v>
+      </c>
+      <c r="D62" s="2" t="n"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Yulduz Moy MChJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>392350013</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000942890894001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2706,14 +2696,14 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №119/26 от 27.07.2026</t>
+          <t>Оплата за транспортные услуги по договору №216/26</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2723,38 +2713,38 @@
       </c>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="n">
-        <v>13987000</v>
+        <v>81589000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Omad Tekstil MChJ</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>382730428</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000878388860001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №178/26 ОТ 27.07.2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №428 11.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2762,40 +2752,40 @@
           <t>154</t>
         </is>
       </c>
-      <c r="C64" s="2" t="n">
-        <v>15244000</v>
-      </c>
-      <c r="D64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="n">
+        <v>103899000</v>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Bog'ishamol Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>346914789</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000442705419001</t>
+          <t>20208000465082397001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Оплата за продукцию по дог. №214/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2803,40 +2793,40 @@
           <t>155</t>
         </is>
       </c>
-      <c r="C65" s="2" t="n">
-        <v>62722000</v>
-      </c>
-      <c r="D65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="n">
+        <v>55133000</v>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Nukus Dori-Darmon XK</t>
+          <t>Bog'ishamol Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>277098460</t>
+          <t>346914789</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000251866498001</t>
+          <t>20208000465082397001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №184/26</t>
+          <t>Tovar uchun to'lov, h/f №3722 12.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2844,40 +2834,40 @@
           <t>156</t>
         </is>
       </c>
-      <c r="C66" s="2" t="n">
-        <v>152783000</v>
-      </c>
-      <c r="D66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="n">
+        <v>39608000</v>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Toshkent Avto Savdo MChJ</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>200251378</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000751791027001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №184/26</t>
+          <t>Оплата за продукцию по договору №279/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2885,23 +2875,23 @@
           <t>157</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n">
-        <v>48141000</v>
-      </c>
+      <c r="C67" s="2" t="n">
+        <v>82118000</v>
+      </c>
+      <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Navro'z Agro MChJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>360863577</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000609062860001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2911,14 +2901,14 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №222/26 ОТ 28.07.2026</t>
+          <t>Оплата за транспортные услуги по дог. №218/26</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2927,39 +2917,39 @@
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>37763000</v>
+        <v>30818000</v>
       </c>
       <c r="D68" s="2" t="n"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Yangi Hayot Agro MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>336608635</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000726090628001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №48/26</t>
+          <t>Социальный налог за июль 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2967,40 +2957,40 @@
           <t>159</t>
         </is>
       </c>
-      <c r="C69" s="2" t="n"/>
-      <c r="D69" s="2" t="n">
-        <v>34836000</v>
-      </c>
+      <c r="C69" s="2" t="n">
+        <v>30818000</v>
+      </c>
+      <c r="D69" s="2" t="n"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1843</t>
+          <t>JShDS iyul oyi chun</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>15.08.2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3009,39 +2999,34 @@
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>68208000</v>
+        <v>152400000</v>
       </c>
       <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Toshkent Avto Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>200251378</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-3948)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000751791027001</t>
+          <t>16307000251586252417</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №250/26</t>
+          <t>Kredit shartnomasi L-2025-3948 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3049,40 +3034,40 @@
           <t>161</t>
         </is>
       </c>
-      <c r="C71" s="2" t="n">
-        <v>102272000</v>
-      </c>
-      <c r="D71" s="2" t="n"/>
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" s="2" t="n">
+        <v>50719000</v>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Savdo MChJ</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>240589170</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000415138551001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №104/26</t>
+          <t>Оплата за продукцию по дог. №237/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3090,40 +3075,40 @@
           <t>162</t>
         </is>
       </c>
-      <c r="C72" s="2" t="n"/>
-      <c r="D72" s="2" t="n">
-        <v>28823000</v>
-      </c>
+      <c r="C72" s="2" t="n">
+        <v>74682000</v>
+      </c>
+      <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Buxoro Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>225137817</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000179102777001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №748 за поставленный товар</t>
+          <t>Предоплата за материалы по договору №240/26</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3132,17 +3117,22 @@
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>300000</v>
+        <v>112370000</v>
       </c>
       <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Navoiy Poligraf XK</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>309846072</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000186649829001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3152,14 +3142,14 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за июль</t>
+          <t>Оплата за упаковочные материалы, с/ф №9318</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3168,39 +3158,39 @@
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>41597000</v>
+        <v>120179000</v>
       </c>
       <c r="D74" s="2" t="n"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Toshkent Avto Savdo MChJ</t>
+          <t>Farg'ona Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>200251378</t>
+          <t>300771412</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000751791027001</t>
+          <t>20208000645340951001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №259/26</t>
+          <t>Предоплата за материалы по договору №187/26</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3209,39 +3199,39 @@
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>77275000</v>
+        <v>171845000</v>
       </c>
       <c r="D75" s="2" t="n"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Toshkent Avto Savdo MChJ</t>
+          <t>Navoiy Poligraf XK</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>200251378</t>
+          <t>309846072</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000751791027001</t>
+          <t>20208000186649829001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №943</t>
+          <t>Оплата за упаковочные материалы, с/ф №9419</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3250,39 +3240,39 @@
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>98982000</v>
+        <v>186321000</v>
       </c>
       <c r="D76" s="2" t="n"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Toshkent Avto Savdo MChJ</t>
+          <t>Shodlik Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>200251378</t>
+          <t>290271954</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000751791027001</t>
+          <t>20208000897054744001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №8514</t>
+          <t>Оплата за упаковочные материалы, с/ф №9589</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3290,40 +3280,40 @@
           <t>167</t>
         </is>
       </c>
-      <c r="C77" s="2" t="n"/>
-      <c r="D77" s="2" t="n">
-        <v>306002000</v>
-      </c>
+      <c r="C77" s="2" t="n">
+        <v>43200000</v>
+      </c>
+      <c r="D77" s="2" t="n"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Buxoro Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>225137817</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000179102777001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4649</t>
+          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №5803</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3333,38 +3323,38 @@
       </c>
       <c r="C78" s="2" t="n"/>
       <c r="D78" s="2" t="n">
-        <v>197237000</v>
+        <v>43866000</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Xiva Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>343761472</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000547477147001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №9341 03.08.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №70/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3372,40 +3362,40 @@
           <t>169</t>
         </is>
       </c>
-      <c r="C79" s="2" t="n">
-        <v>8345000</v>
-      </c>
-      <c r="D79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n">
+        <v>34356000</v>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Toshkent Avto Savdo MChJ</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>200251378</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000751791027001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №30/26</t>
+          <t>Оплата за товар по счет-фактуре №1061 от 19.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3414,22 +3404,22 @@
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>13589000</v>
+        <v>47449000</v>
       </c>
       <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Toshkent Avto Savdo MChJ</t>
+          <t>Oltin Vodiy Mato MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>200251378</t>
+          <t>258917044</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000751791027001</t>
+          <t>20208000513855120001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3439,14 +3429,14 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №228/26</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №81/26</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3456,38 +3446,38 @@
       </c>
       <c r="C81" s="2" t="n"/>
       <c r="D81" s="2" t="n">
-        <v>60385000</v>
+        <v>72977000</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Farg'ona Sut Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>273042818</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000838886010001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4083 от 05.08.2026, в т.ч. НДС 12%</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №108/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3497,38 +3487,38 @@
       </c>
       <c r="C82" s="2" t="n"/>
       <c r="D82" s="2" t="n">
-        <v>46971000</v>
+        <v>67518000</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sarbon Metall MChJ</t>
+          <t>Qo'qon Plastik MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>224962188</t>
+          <t>287935800</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000018250957001</t>
+          <t>20208000515428065001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №178/26 от 06.08.2026</t>
+          <t>Tovar uchun to'lov, h/f №9037 20.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3538,38 +3528,38 @@
       </c>
       <c r="C83" s="2" t="n"/>
       <c r="D83" s="2" t="n">
-        <v>23308000</v>
+        <v>33779000</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Navro'z Avto Savdo AJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>222534623</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000568781793001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3520</t>
+          <t>Оплата за товар по счет-фактуре №4790 от 20.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3578,39 +3568,39 @@
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>21847000</v>
+        <v>647902000</v>
       </c>
       <c r="D84" s="2" t="n"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Nukus Dori-Darmon XK</t>
+          <t>Yulduz Moy MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>277098460</t>
+          <t>392350013</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000251866498001</t>
+          <t>20208000942890894001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №8335</t>
+          <t>Оплата за товары согласно счет-фактуре №3703</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3618,35 +3608,40 @@
           <t>175</t>
         </is>
       </c>
-      <c r="C85" s="2" t="n">
-        <v>225995000</v>
-      </c>
-      <c r="D85" s="2" t="n"/>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n">
+        <v>124492000</v>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Qo'qon Plastik MChJ</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>287935800</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000515428065001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №1446</t>
+          <t>Shartnoma №282/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3656,38 +3651,38 @@
       </c>
       <c r="C86" s="2" t="n"/>
       <c r="D86" s="2" t="n">
-        <v>55702000</v>
+        <v>51229000</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Plastik MChJ</t>
+          <t>Toshkent Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>290662356</t>
+          <t>240191920</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000062492032001</t>
+          <t>20208000041651902001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8103 за поставленный товар</t>
+          <t>Предоплата за товар по договору №238/26 от 24.08.2026</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3695,40 +3690,40 @@
           <t>177</t>
         </is>
       </c>
-      <c r="C87" s="2" t="n">
-        <v>9183000</v>
-      </c>
-      <c r="D87" s="2" t="n"/>
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="2" t="n">
+        <v>50343000</v>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Toshkent Avto Savdo MChJ</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>200251378</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000751791027001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6265</t>
+          <t>Оплата за продукцию по договору №214/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3736,40 +3731,40 @@
           <t>178</t>
         </is>
       </c>
-      <c r="C88" s="2" t="n">
-        <v>12704000</v>
-      </c>
-      <c r="D88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n">
+        <v>25592000</v>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Toshkent Avto Savdo MChJ</t>
+          <t>Bog'ishamol Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>200251378</t>
+          <t>346914789</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000751791027001</t>
+          <t>20208000465082397001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №106/26, QQS bilan</t>
+          <t>Оплата за продукцию по договору №111/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3777,40 +3772,40 @@
           <t>179</t>
         </is>
       </c>
-      <c r="C89" s="2" t="n">
-        <v>13746000</v>
-      </c>
-      <c r="D89" s="2" t="n"/>
+      <c r="C89" s="2" t="n"/>
+      <c r="D89" s="2" t="n">
+        <v>24836000</v>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Nukus Dori-Darmon XK</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>277098460</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000251866498001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №142/26</t>
+          <t>Оплата за продукцию по договору №212/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3819,39 +3814,39 @@
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>13805000</v>
+        <v>15490000</v>
       </c>
       <c r="D90" s="2" t="n"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Yangi Hayot Dori-Darmon MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>372599213</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000876079668001</t>
+          <t>20208000227154788001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №46/26</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3860,39 +3855,39 @@
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>24784000</v>
+        <v>41839000</v>
       </c>
       <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Navro'z Qurilish Materiallari MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>254190271</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000548897054001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Аренда помещения за август, дог. №32/25</t>
+          <t>QQS iyul 2026 uchun</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3901,39 +3896,39 @@
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>29402000</v>
+        <v>45305000</v>
       </c>
       <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Nukus Dori-Darmon XK</t>
+          <t>Navoiy Poligraf XK</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>277098460</t>
+          <t>309846072</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000251866498001</t>
+          <t>20208000186649829001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №3425</t>
+          <t>Оплата за транспортные услуги по договору №234/26</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3943,38 +3938,38 @@
       </c>
       <c r="C93" s="2" t="n"/>
       <c r="D93" s="2" t="n">
-        <v>398867000</v>
+        <v>110438000</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Toshkent Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>240191920</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000041651902001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2105 от 11.08.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №32/26 от 26.08.2026</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3982,40 +3977,40 @@
           <t>184</t>
         </is>
       </c>
-      <c r="C94" s="2" t="n"/>
-      <c r="D94" s="2" t="n">
-        <v>190418000</v>
-      </c>
+      <c r="C94" s="2" t="n">
+        <v>32126000</v>
+      </c>
+      <c r="D94" s="2" t="n"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Buxoro Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>225137817</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000179102777001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №2031 за поставленный товар</t>
+          <t>Оплата за транспортные услуги по договору №189/26</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4025,38 +4020,38 @@
       </c>
       <c r="C95" s="2" t="n"/>
       <c r="D95" s="2" t="n">
-        <v>31683000</v>
+        <v>924791000</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Chust Agro MChJ</t>
+          <t>Marg'ilon Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>262401919</t>
+          <t>223624727</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000060416519001</t>
+          <t>20208000373641798001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №95/26 от 12.08.2026</t>
+          <t>Оплата за товар по счет-фактуре №4924 от 27.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>13.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4064,40 +4059,40 @@
           <t>186</t>
         </is>
       </c>
-      <c r="C96" s="2" t="n"/>
-      <c r="D96" s="2" t="n">
-        <v>166992000</v>
-      </c>
+      <c r="C96" s="2" t="n">
+        <v>50801000</v>
+      </c>
+      <c r="D96" s="2" t="n"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Buxoro Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>225137817</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000179102777001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7499 13.08.2026, QQS bilan</t>
+          <t>Оплата за транспортные услуги по договору №183/26</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>13.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4106,39 +4101,39 @@
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>23625000</v>
+        <v>175463000</v>
       </c>
       <c r="D97" s="2" t="n"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Nukus Dori-Darmon XK</t>
+          <t>Buxoro Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>277098460</t>
+          <t>225137817</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000251866498001</t>
+          <t>20208000179102777001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №5582</t>
+          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО С/Ф №2357</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>13.08.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4146,40 +4141,40 @@
           <t>188</t>
         </is>
       </c>
-      <c r="C98" s="2" t="n">
-        <v>60077000</v>
-      </c>
-      <c r="D98" s="2" t="n"/>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n">
+        <v>721683000</v>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Toshkent Avto Savdo MChJ</t>
+          <t>Bog'ishamol Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>200251378</t>
+          <t>346914789</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000751791027001</t>
+          <t>20208000465082397001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №2615</t>
+          <t>Предоплата за товар по договору №227/26 от 28.08.2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4187,40 +4182,40 @@
           <t>189</t>
         </is>
       </c>
-      <c r="C99" s="2" t="n"/>
-      <c r="D99" s="2" t="n">
-        <v>128777000</v>
-      </c>
+      <c r="C99" s="2" t="n">
+        <v>110828000</v>
+      </c>
+      <c r="D99" s="2" t="n"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Navoiy Poligraf XK</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>309846072</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000186649829001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №266/26, НДС 12%</t>
+          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №22/26, QQS BILAN</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4228,23 +4223,23 @@
           <t>190</t>
         </is>
       </c>
-      <c r="C100" s="2" t="n"/>
-      <c r="D100" s="2" t="n">
-        <v>92235000</v>
-      </c>
+      <c r="C100" s="2" t="n">
+        <v>139716000</v>
+      </c>
+      <c r="D100" s="2" t="n"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Navro'z Agro MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>360863577</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000609062860001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4254,14 +4249,14 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №146/26 от 14.08.2026</t>
+          <t>Оплата за транспортные услуги по договору №2/26</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4271,38 +4266,38 @@
       </c>
       <c r="C101" s="2" t="n"/>
       <c r="D101" s="2" t="n">
-        <v>33811000</v>
+        <v>220767000</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №28/26 от 14.08.2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №201/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4310,40 +4305,40 @@
           <t>192</t>
         </is>
       </c>
-      <c r="C102" s="2" t="n">
-        <v>54140000</v>
-      </c>
-      <c r="D102" s="2" t="n"/>
+      <c r="C102" s="2" t="n"/>
+      <c r="D102" s="2" t="n">
+        <v>43499000</v>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Toshkent Avto Savdo MChJ</t>
+          <t>Toshkent Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>200251378</t>
+          <t>240191920</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000751791027001</t>
+          <t>20208000041651902001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6398</t>
+          <t>Оплата за товар по счет-фактуре №1848 от 31.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>15.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4351,35 +4346,40 @@
           <t>193</t>
         </is>
       </c>
-      <c r="C103" s="2" t="n">
-        <v>152400000</v>
-      </c>
-      <c r="D103" s="2" t="n"/>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n">
+        <v>37234000</v>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-3948)</t>
+          <t>Navro'z Polimer MChJ</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>16307000251586252417</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-3948 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Оплата за товар по счет-фактуре №6241 от 31.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4387,40 +4387,35 @@
           <t>194</t>
         </is>
       </c>
-      <c r="C104" s="2" t="n"/>
-      <c r="D104" s="2" t="n">
-        <v>114154000</v>
-      </c>
+      <c r="C104" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>305246474</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2084 за поставленный товар</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4428,40 +4423,40 @@
           <t>195</t>
         </is>
       </c>
-      <c r="C105" s="2" t="n"/>
-      <c r="D105" s="2" t="n">
-        <v>99491000</v>
-      </c>
+      <c r="C105" s="2" t="n">
+        <v>32725000</v>
+      </c>
+      <c r="D105" s="2" t="n"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz AJ</t>
+          <t>Oltin Vodiy Mato MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>263236247</t>
+          <t>258917044</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000703736417001</t>
+          <t>20208000513855120001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №287/26 от 17.08.2026</t>
+          <t>Оплата за упаковочные материалы, с/ф №8378</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4469,40 +4464,40 @@
           <t>196</t>
         </is>
       </c>
-      <c r="C106" s="2" t="n"/>
-      <c r="D106" s="2" t="n">
-        <v>78172000</v>
-      </c>
+      <c r="C106" s="2" t="n">
+        <v>100646000</v>
+      </c>
+      <c r="D106" s="2" t="n"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Buxoro Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>225137817</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000179102777001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9942 от 17.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за сырье по договору №286/26 от 31.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4510,40 +4505,40 @@
           <t>197</t>
         </is>
       </c>
-      <c r="C107" s="2" t="n"/>
-      <c r="D107" s="2" t="n">
-        <v>45684000</v>
-      </c>
+      <c r="C107" s="2" t="n">
+        <v>57407000</v>
+      </c>
+      <c r="D107" s="2" t="n"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Navoiy Poligraf XK</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>309846072</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000186649829001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8607 от 17.08.2026, в т.ч. НДС 12%</t>
+          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №38/26</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4553,38 +4548,38 @@
       </c>
       <c r="C108" s="2" t="n"/>
       <c r="D108" s="2" t="n">
-        <v>42424000</v>
+        <v>37762000</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Chust Agro MChJ</t>
+          <t>Bog'ishamol Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>262401919</t>
+          <t>346914789</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000060416519001</t>
+          <t>20208000465082397001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №205/26 от 17.08.2026</t>
+          <t>Оплата по счет-фактуре №5508 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4592,40 +4587,35 @@
           <t>199</t>
         </is>
       </c>
-      <c r="C109" s="2" t="n"/>
-      <c r="D109" s="2" t="n">
-        <v>37901000</v>
-      </c>
+      <c r="C109" s="2" t="n">
+        <v>202470000</v>
+      </c>
+      <c r="D109" s="2" t="n"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Omad Tekstil MChJ</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>382730428</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000878388860001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №187/26, НДС 12%</t>
+          <t>ПЕРЕЧИСЛЕНИЕ ЗАРАБОТНОЙ ПЛАТЫ ЗА АВГУСТ 2026 Г. СОГЛАСНО РЕЕСТРУ №94</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4633,40 +4623,40 @@
           <t>200</t>
         </is>
       </c>
-      <c r="C110" s="2" t="n"/>
-      <c r="D110" s="2" t="n">
-        <v>28879000</v>
-      </c>
+      <c r="C110" s="2" t="n">
+        <v>304710000</v>
+      </c>
+      <c r="D110" s="2" t="n"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Oltin Vodiy Mato MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>258917044</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000513855120001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №15/26, НДС 12%</t>
+          <t>Оплата за сырье по договору №283/26 от 04.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4674,40 +4664,40 @@
           <t>201</t>
         </is>
       </c>
-      <c r="C111" s="2" t="n">
-        <v>30818000</v>
-      </c>
-      <c r="D111" s="2" t="n"/>
+      <c r="C111" s="2" t="n"/>
+      <c r="D111" s="2" t="n">
+        <v>208129000</v>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Социальный налог за июль 2026 г.</t>
+          <t>Оплата по счет-фактуре №5221 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4715,40 +4705,40 @@
           <t>202</t>
         </is>
       </c>
-      <c r="C112" s="2" t="n">
-        <v>30818000</v>
-      </c>
-      <c r="D112" s="2" t="n"/>
+      <c r="C112" s="2" t="n"/>
+      <c r="D112" s="2" t="n">
+        <v>138115000</v>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июль 2026 г.</t>
+          <t>Оплата за продукцию по дог. №211/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4756,40 +4746,40 @@
           <t>203</t>
         </is>
       </c>
-      <c r="C113" s="2" t="n">
-        <v>47766000</v>
-      </c>
-      <c r="D113" s="2" t="n"/>
+      <c r="C113" s="2" t="n"/>
+      <c r="D113" s="2" t="n">
+        <v>130401000</v>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Savdo MChJ</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>240589170</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000415138551001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №99/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №64/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4799,38 +4789,38 @@
       </c>
       <c r="C114" s="2" t="n"/>
       <c r="D114" s="2" t="n">
-        <v>187795000</v>
+        <v>70281000</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №29/26, НДС 12%</t>
+          <t>Оплата за товар по с/ф №3437 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4840,38 +4830,38 @@
       </c>
       <c r="C115" s="2" t="n"/>
       <c r="D115" s="2" t="n">
-        <v>17280000</v>
+        <v>70208000</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona MChJ</t>
+          <t>Xiva Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>283144992</t>
+          <t>343761472</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000168364427001</t>
+          <t>20208000547477147001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №37/26 от 18.08.2026</t>
+          <t>Оплата за товар по счет-фактуре №6441 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4881,38 +4871,38 @@
       </c>
       <c r="C116" s="2" t="n"/>
       <c r="D116" s="2" t="n">
-        <v>20133000</v>
+        <v>54164000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Omad Tekstil MChJ</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>382730428</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000878388860001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9556</t>
+          <t>Shartnoma №240/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4920,40 +4910,40 @@
           <t>207</t>
         </is>
       </c>
-      <c r="C117" s="2" t="n">
-        <v>7799000</v>
-      </c>
-      <c r="D117" s="2" t="n"/>
+      <c r="C117" s="2" t="n"/>
+      <c r="D117" s="2" t="n">
+        <v>52696000</v>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Toshkent Avto Savdo MChJ</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>200251378</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000751791027001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №5369</t>
+          <t>Оплата за продукцию по договору №124/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4961,40 +4951,40 @@
           <t>208</t>
         </is>
       </c>
-      <c r="C118" s="2" t="n">
-        <v>20707000</v>
-      </c>
-      <c r="D118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n">
+        <v>45242000</v>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Yangi Hayot Dori-Darmon MChJ</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>372599213</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000876079668001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №244/26</t>
+          <t>Оплата за товар по счет-фактуре №9777 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5002,40 +4992,40 @@
           <t>209</t>
         </is>
       </c>
-      <c r="C119" s="2" t="n">
-        <v>36469000</v>
-      </c>
-      <c r="D119" s="2" t="n"/>
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" s="2" t="n">
+        <v>34580000</v>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Savdo MChJ</t>
+          <t>Toshkent Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>240589170</t>
+          <t>240191920</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000415138551001</t>
+          <t>20208000041651902001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги п договору №27/26</t>
+          <t>Предоплата за товар по договору №150/26 от 07.09.2026</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5043,40 +5033,40 @@
           <t>210</t>
         </is>
       </c>
-      <c r="C120" s="2" t="n"/>
-      <c r="D120" s="2" t="n">
-        <v>16221000</v>
-      </c>
+      <c r="C120" s="2" t="n">
+        <v>66879000</v>
+      </c>
+      <c r="D120" s="2" t="n"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Jizzax Plastik AJ</t>
+          <t>Navoiy Poligraf XK</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>261879358</t>
+          <t>309846072</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000005154280001</t>
+          <t>20208000186649829001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3703 от 20.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №238/26</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5084,40 +5074,40 @@
           <t>211</t>
         </is>
       </c>
-      <c r="C121" s="2" t="n"/>
-      <c r="D121" s="2" t="n">
-        <v>107410000</v>
-      </c>
+      <c r="C121" s="2" t="n">
+        <v>94979000</v>
+      </c>
+      <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Navoiy Qog'oz AJ</t>
+          <t>Buxoro Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>263236247</t>
+          <t>225137817</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000703736417001</t>
+          <t>20208000179102777001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7763 за поставенный товар</t>
+          <t>Оплата за транспортные услуги по дог. №172/26</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5125,40 +5115,40 @@
           <t>212</t>
         </is>
       </c>
-      <c r="C122" s="2" t="n">
-        <v>23450000</v>
-      </c>
-      <c r="D122" s="2" t="n"/>
+      <c r="C122" s="2" t="n"/>
+      <c r="D122" s="2" t="n">
+        <v>251478000</v>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Toshkent Avto Savdo MChJ</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>200251378</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000751791027001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №1259</t>
+          <t>Предоплата за товар по договору №236/26 от 08.09.2026</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5168,38 +5158,38 @@
       </c>
       <c r="C123" s="2" t="n"/>
       <c r="D123" s="2" t="n">
-        <v>352296000</v>
+        <v>139015000</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Chust Agro MChJ</t>
+          <t>Marg'ilon Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>262401919</t>
+          <t>223624727</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000060416519001</t>
+          <t>20208000373641798001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6414 за поставленный товар</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №6483 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5207,40 +5197,40 @@
           <t>214</t>
         </is>
       </c>
-      <c r="C124" s="2" t="n">
-        <v>9057000</v>
-      </c>
-      <c r="D124" s="2" t="n"/>
+      <c r="C124" s="2" t="n"/>
+      <c r="D124" s="2" t="n">
+        <v>94038000</v>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Toshkent Avto Savdo MChJ</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>200251378</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000751791027001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №1393</t>
+          <t>Предоплата за товар по договору №147/26 от 08.09.2026</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5249,39 +5239,39 @@
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>41291000</v>
+        <v>78650000</v>
       </c>
       <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Navoiy Poligraf XK</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>309846072</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000186649829001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>QQS iyul 2026 uchun</t>
+          <t>Оплата за товары согласно счет-фактуре №7326</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5289,23 +5279,23 @@
           <t>216</t>
         </is>
       </c>
-      <c r="C126" s="2" t="n">
-        <v>645777000</v>
-      </c>
-      <c r="D126" s="2" t="n"/>
+      <c r="C126" s="2" t="n"/>
+      <c r="D126" s="2" t="n">
+        <v>44206000</v>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Yangi Hayot Agro MChJ</t>
+          <t>Farg'ona Sut Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>336608635</t>
+          <t>273042818</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000726090628001</t>
+          <t>20208000838886010001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5315,14 +5305,14 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №5327</t>
+          <t>Оплата по с/ф №6324 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5331,22 +5321,22 @@
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>1838597000</v>
+        <v>22204000</v>
       </c>
       <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Toshkent Avto Savdo MChJ</t>
+          <t>Bahor Qurilish Materiallari AJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>200251378</t>
+          <t>230192105</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000751791027001</t>
+          <t>20208000971885157001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5356,14 +5346,14 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №7453</t>
+          <t>Аренда помещения за сентябрь, дог. №12/21</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5371,40 +5361,40 @@
           <t>218</t>
         </is>
       </c>
-      <c r="C128" s="2" t="n"/>
-      <c r="D128" s="2" t="n">
-        <v>31026000</v>
-      </c>
+      <c r="C128" s="2" t="n">
+        <v>74725000</v>
+      </c>
+      <c r="D128" s="2" t="n"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Navoiy Poligraf XK</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>309846072</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000186649829001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1610 за поставленный товар</t>
+          <t>Оплата за товары согласно счет-фактуре №6558</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5413,39 +5403,39 @@
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>15490000</v>
+        <v>112289000</v>
       </c>
       <c r="D129" s="2" t="n"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Navoiy Poligraf XK</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>309846072</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000442705419001</t>
+          <t>20208000186649829001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №116/26</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5453,40 +5443,40 @@
           <t>220</t>
         </is>
       </c>
-      <c r="C130" s="2" t="n">
-        <v>15874000</v>
-      </c>
-      <c r="D130" s="2" t="n"/>
+      <c r="C130" s="2" t="n"/>
+      <c r="D130" s="2" t="n">
+        <v>208564000</v>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Nurafshon Oziq-ovqat Savdo MChJ</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>216007714</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000266453409001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №139/26, QQS bilan</t>
+          <t>Оплата за товар по с/ф №4944 от 14.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5496,38 +5486,38 @@
       </c>
       <c r="C131" s="2" t="n"/>
       <c r="D131" s="2" t="n">
-        <v>159123000</v>
+        <v>91164000</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Farg'ona Sut Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>273042818</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000838886010001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №183/26 от 27.08.2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №276/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5535,40 +5525,40 @@
           <t>222</t>
         </is>
       </c>
-      <c r="C132" s="2" t="n"/>
-      <c r="D132" s="2" t="n">
-        <v>38300000</v>
-      </c>
+      <c r="C132" s="2" t="n">
+        <v>32504000</v>
+      </c>
+      <c r="D132" s="2" t="n"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Buxoro Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>225137817</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000179102777001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №112/26, НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №1888</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5576,23 +5566,23 @@
           <t>223</t>
         </is>
       </c>
-      <c r="C133" s="2" t="n"/>
-      <c r="D133" s="2" t="n">
-        <v>36082000</v>
-      </c>
+      <c r="C133" s="2" t="n">
+        <v>42632000</v>
+      </c>
+      <c r="D133" s="2" t="n"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Yulduz Moy MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>392350013</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000942890894001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5602,14 +5592,14 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9173 от 27.08.2026, в т.ч. НДС 12%</t>
+          <t>Tovarlar uchun to'lov h/f №6637</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5617,40 +5607,35 @@
           <t>224</t>
         </is>
       </c>
-      <c r="C134" s="2" t="n"/>
-      <c r="D134" s="2" t="n">
-        <v>17713000</v>
-      </c>
+      <c r="C134" s="2" t="n">
+        <v>152400000</v>
+      </c>
+      <c r="D134" s="2" t="n"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>305246474</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-3948)</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>16307000251586252417</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №6514 за поставленный товар</t>
+          <t>Kredit shartnomasi L-2025-3948 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5658,40 +5643,40 @@
           <t>225</t>
         </is>
       </c>
-      <c r="C135" s="2" t="n"/>
-      <c r="D135" s="2" t="n">
-        <v>69726000</v>
-      </c>
+      <c r="C135" s="2" t="n">
+        <v>27610000</v>
+      </c>
+      <c r="D135" s="2" t="n"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактре №4633 от 28.08.2026, в т.ч. НДС 12%</t>
+          <t>Социальный налог за август 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5699,40 +5684,40 @@
           <t>226</t>
         </is>
       </c>
-      <c r="C136" s="2" t="n"/>
-      <c r="D136" s="2" t="n">
-        <v>53458000</v>
-      </c>
+      <c r="C136" s="2" t="n">
+        <v>27610000</v>
+      </c>
+      <c r="D136" s="2" t="n"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Nurafshon Non MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>336469147</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000994650823001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1375 за поставленный товар</t>
+          <t>НДФЛ за август 2026</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5742,38 +5727,38 @@
       </c>
       <c r="C137" s="2" t="n"/>
       <c r="D137" s="2" t="n">
-        <v>36569000</v>
+        <v>145180000</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №9623 28.08.2026, QQS BILAN</t>
+          <t>Оплата за товар по счет-фактуре №8277 от 17.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5783,38 +5768,38 @@
       </c>
       <c r="C138" s="2" t="n"/>
       <c r="D138" s="2" t="n">
-        <v>103267000</v>
+        <v>113994000</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Chust Agro MChJ</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>262401919</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000060416519001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №57/26 от 31.08.2026</t>
+          <t>Оплата за продукцию по договору №91/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5824,38 +5809,38 @@
       </c>
       <c r="C139" s="2" t="n"/>
       <c r="D139" s="2" t="n">
-        <v>15446000</v>
+        <v>54339000</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Bog'ishamol Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>346914789</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000465082397001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №182/26, QQS 12%</t>
+          <t>Предоплата за товар по дог. №251/26 от 17.09.2026</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5863,35 +5848,40 @@
           <t>230</t>
         </is>
       </c>
-      <c r="C140" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D140" s="2" t="n"/>
+      <c r="C140" s="2" t="n"/>
+      <c r="D140" s="2" t="n">
+        <v>40430000</v>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Navro'z Polimer MChJ</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Плата за SMS-информирование</t>
+          <t>Shartnoma №234/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5900,39 +5890,39 @@
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>45660000</v>
+        <v>46046000</v>
       </c>
       <c r="D141" s="2" t="n"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Toshkent Avto Savdo MChJ</t>
+          <t>Buxoro Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>200251378</t>
+          <t>225137817</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000751791027001</t>
+          <t>20208000179102777001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Оплата за сыье по дог. №269/26 от 31.08.2026, НДС 12%</t>
+          <t>Оплата за сырье по договору №217/26 от 17.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>01.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5940,40 +5930,40 @@
           <t>232</t>
         </is>
       </c>
-      <c r="C142" s="2" t="n">
-        <v>190747000</v>
-      </c>
-      <c r="D142" s="2" t="n"/>
+      <c r="C142" s="2" t="n"/>
+      <c r="D142" s="2" t="n">
+        <v>272389000</v>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Nurafshon Oziq-ovqat Savdo MChJ</t>
+          <t>Toshkent Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>216007714</t>
+          <t>240191920</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000266453409001</t>
+          <t>20208000041651902001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №9155</t>
+          <t>Предоплата за товар по договору №84/26 от 18.09.2026</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5983,38 +5973,38 @@
       </c>
       <c r="C143" s="2" t="n"/>
       <c r="D143" s="2" t="n">
-        <v>58304000</v>
+        <v>40013000</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Omad Tekstil MChJ</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>382730428</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000878388860001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №121/26, НДС 12%</t>
+          <t>Shartnoma №270/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6022,40 +6012,40 @@
           <t>234</t>
         </is>
       </c>
-      <c r="C144" s="2" t="n"/>
-      <c r="D144" s="2" t="n">
-        <v>49167000</v>
-      </c>
+      <c r="C144" s="2" t="n">
+        <v>27009000</v>
+      </c>
+      <c r="D144" s="2" t="n"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Farg'ona Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>300771412</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000645340951001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №7199 02.09.2026, QQS BILAN</t>
+          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №9253</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6063,40 +6053,40 @@
           <t>235</t>
         </is>
       </c>
-      <c r="C145" s="2" t="n"/>
-      <c r="D145" s="2" t="n">
-        <v>129082000</v>
-      </c>
+      <c r="C145" s="2" t="n">
+        <v>45297000</v>
+      </c>
+      <c r="D145" s="2" t="n"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Buxoro Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>225137817</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000179102777001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №259/26, НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №2133</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6104,40 +6094,40 @@
           <t>236</t>
         </is>
       </c>
-      <c r="C146" s="2" t="n"/>
-      <c r="D146" s="2" t="n">
-        <v>48912000</v>
-      </c>
+      <c r="C146" s="2" t="n">
+        <v>904031000</v>
+      </c>
+      <c r="D146" s="2" t="n"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Chust Agro MChJ</t>
+          <t>Buxoro Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>262401919</t>
+          <t>225137817</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000060416519001</t>
+          <t>20208000179102777001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №293/26, НДС 12%</t>
+          <t>Оплата за транспортные услуги по дог. №251/26</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6145,40 +6135,40 @@
           <t>237</t>
         </is>
       </c>
-      <c r="C147" s="2" t="n">
-        <v>80481000</v>
-      </c>
-      <c r="D147" s="2" t="n"/>
+      <c r="C147" s="2" t="n"/>
+      <c r="D147" s="2" t="n">
+        <v>451325000</v>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Yangi Hayot Dori-Darmon MChJ</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>372599213</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000876079668001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №108/26 от 04.09.2026, НДС 12%</t>
+          <t>Оплата за продукцию по договору №47/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6186,40 +6176,40 @@
           <t>238</t>
         </is>
       </c>
-      <c r="C148" s="2" t="n"/>
-      <c r="D148" s="2" t="n">
-        <v>319963000</v>
-      </c>
+      <c r="C148" s="2" t="n">
+        <v>37747000</v>
+      </c>
+      <c r="D148" s="2" t="n"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №278/26, QQS 12%</t>
+          <t>QQS avgust 2026 uchun</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>24.09.2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6229,38 +6219,38 @@
       </c>
       <c r="C149" s="2" t="n"/>
       <c r="D149" s="2" t="n">
-        <v>92133000</v>
+        <v>49678000</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Chust Agro MChJ</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>262401919</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000060416519001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №55/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №4874 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6268,23 +6258,23 @@
           <t>240</t>
         </is>
       </c>
-      <c r="C150" s="2" t="n"/>
-      <c r="D150" s="2" t="n">
-        <v>57729000</v>
-      </c>
+      <c r="C150" s="2" t="n">
+        <v>13878000</v>
+      </c>
+      <c r="D150" s="2" t="n"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>305246474</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>20208000227154788001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -6294,14 +6284,14 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2866 от 07.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6309,40 +6299,40 @@
           <t>241</t>
         </is>
       </c>
-      <c r="C151" s="2" t="n">
-        <v>27289000</v>
-      </c>
-      <c r="D151" s="2" t="n"/>
+      <c r="C151" s="2" t="n"/>
+      <c r="D151" s="2" t="n">
+        <v>197530000</v>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Farovon Avto Ehtiyot MChJ</t>
+          <t>Navro'z Polimer MChJ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>241299705</t>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000573505794001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №200/26 от 07.09.2026, НДС 12%</t>
+          <t>Оплата за продукцию по договору №76/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>29.09.2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6351,39 +6341,39 @@
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>65095000</v>
+        <v>117627000</v>
       </c>
       <c r="D152" s="2" t="n"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Toshkent Avto Savdo MChJ</t>
+          <t>Navoiy Poligraf XK</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>200251378</t>
+          <t>309846072</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000751791027001</t>
+          <t>20208000186649829001</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №1021</t>
+          <t>Оплата за товары согласно с/ф №673</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6391,35 +6381,40 @@
           <t>243</t>
         </is>
       </c>
-      <c r="C153" s="2" t="n">
-        <v>202470000</v>
-      </c>
-      <c r="D153" s="2" t="n"/>
+      <c r="C153" s="2" t="n"/>
+      <c r="D153" s="2" t="n">
+        <v>110653000</v>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Navro'z Polimer MChJ</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>324647426</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000643332559001</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Tovar uchun to'lov, h/f №8088 30.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -6427,40 +6422,35 @@
           <t>244</t>
         </is>
       </c>
-      <c r="C154" s="2" t="n"/>
-      <c r="D154" s="2" t="n">
-        <v>139356000</v>
-      </c>
+      <c r="C154" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D154" s="2" t="n"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>305246474</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20208000686433325001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9862 08.09.2026, QQS bilan</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -6469,1524 +6459,58 @@
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>22204000</v>
+        <v>606096000</v>
       </c>
       <c r="D155" s="2" t="n"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Navro'z Qurilish Materiallari MChJ</t>
+          <t>Navoiy Poligraf XK</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>254190271</t>
+          <t>309846072</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>20208000548897054001</t>
+          <t>20208000186649829001</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Аренда помещения за сентябрь, дог. №32/25</t>
+          <t>Предоплата за материалы по договору №274/26</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="n">
-        <v>58119000</v>
-      </c>
-      <c r="D156" s="2" t="n"/>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Kattaqo'rg'on Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>240589170</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>20208000415138551001</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>Оплата за сырье по дог. №71/26 от 08.09.2026, НДС 12%</t>
-        </is>
+          <t>Jami aylanma:</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="n">
+        <v>10013298000</v>
+      </c>
+      <c r="D156" s="4" t="n">
+        <v>9971298000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="n"/>
-      <c r="D157" s="2" t="n">
-        <v>94584000</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Qo'qon Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>305246474</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>20208000686433325001</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №4773 за поставленный товар</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>09.09.2026</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="n">
-        <v>45550000</v>
-      </c>
-      <c r="D158" s="2" t="n"/>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Toshkent Avto Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>200251378</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>20208000751791027001</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>Оплата за транспортные услуги по дог. №189/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>10.09.2026</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="n">
-        <v>59350000</v>
-      </c>
-      <c r="D159" s="2" t="n"/>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Toshkent Avto Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>200251378</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>20208000751791027001</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>Предоплата за материалы по договору №194/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>14.09.2026</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="n"/>
-      <c r="D160" s="2" t="n">
-        <v>558249000</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Qo'qon Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>305246474</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>20208000686433325001</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>Shartnoma №201/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>14.09.2026</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="n">
-        <v>59108000</v>
-      </c>
-      <c r="D161" s="2" t="n"/>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Yangi Hayot Dori-Darmon MChJ</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>372599213</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>20208000876079668001</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>Предоплата за материалы по дог. №9/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>14.09.2026</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="n">
-        <v>248922000</v>
-      </c>
-      <c r="D162" s="2" t="n"/>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Yangi Hayot Dori-Darmon MChJ</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>372599213</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>20208000876079668001</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №249/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>15.09.2026</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="n"/>
-      <c r="D163" s="2" t="n">
-        <v>60485000</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Qo'qon Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>305246474</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>20208000686433325001</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>Оплата за товар по счет-фактуре №6301 от 15.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>15.09.2026</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="n">
-        <v>152400000</v>
-      </c>
-      <c r="D164" s="2" t="n"/>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-3948)</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>16307000251586252417</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>Kredit shartnomasi L-2025-3948 bo'yicha navbatdagi to'lov (09.2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>15.09.2026</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="n">
-        <v>517385000</v>
-      </c>
-      <c r="D165" s="2" t="n"/>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Toshkent Avto Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>200251378</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>20208000751791027001</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>Оплата за сырье по договору №293/26 от 15.09.2026, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>16.09.2026</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="n"/>
-      <c r="D166" s="2" t="n">
-        <v>109371000</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Qo'qon Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>305246474</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>20208000686433325001</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>Оплата за товар по с/ф №1076 от 16.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>16.09.2026</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="n"/>
-      <c r="D167" s="2" t="n">
-        <v>78108000</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Jizzax Plastik AJ</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>261879358</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>20208000005154280001</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №7034 ОТ 16.09.2026, В Т.Ч. НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>16.09.2026</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="n">
-        <v>27610000</v>
-      </c>
-      <c r="D168" s="2" t="n"/>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>Социальный налог за август 2026 г.</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>16.09.2026</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="n">
-        <v>27610000</v>
-      </c>
-      <c r="D169" s="2" t="n"/>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>Налог на доходы физических лиц за август 2026 г.</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>16.09.2026</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="n">
-        <v>116491000</v>
-      </c>
-      <c r="D170" s="2" t="n"/>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>Toshkent Avto Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>200251378</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>20208000751791027001</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>Оплата за транспортные услуги по договору №224/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>18.09.2026</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="n"/>
-      <c r="D171" s="2" t="n">
-        <v>191473000</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Qo'qon Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>305246474</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>20208000686433325001</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6217 18.09.2026, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="n"/>
-      <c r="D172" s="2" t="n">
-        <v>159741000</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Qo'qon Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>305246474</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>20208000686433325001</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>Shartnoma №26/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="n"/>
-      <c r="D173" s="2" t="n">
-        <v>135238000</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Qo'qon Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>305246474</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>20208000686433325001</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>Оплата за товар по счет-фактуре №8533 от 21.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="n"/>
-      <c r="D174" s="2" t="n">
-        <v>53788000</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Omad Tekstil MChJ</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>382730428</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>20208000878388860001</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №190/26 от 21.09.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="n">
-        <v>37276000</v>
-      </c>
-      <c r="D175" s="2" t="n"/>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>Yangi Hayot Dori-Darmon MChJ</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>372599213</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>20208000876079668001</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>Оплата за товары согласно счет-фактуре №8118</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="n">
-        <v>345897000</v>
-      </c>
-      <c r="D176" s="2" t="n"/>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Nukus Dori-Darmon XK</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>277098460</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>20208000251866498001</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>Оплата за товары согласно счет-фактуре №6029</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>22.09.2026</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="n"/>
-      <c r="D177" s="2" t="n">
-        <v>112093000</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Omad Tekstil MChJ</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>382730428</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>20208000878388860001</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>Оплата за товар по с/ф №3590 от 22.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>22.09.2026</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="n">
-        <v>30227000</v>
-      </c>
-      <c r="D178" s="2" t="n"/>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Yangi Hayot Dori-Darmon MChJ</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>372599213</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>20208000876079668001</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГОВОРУ №212/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>23.09.2026</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="n"/>
-      <c r="D179" s="2" t="n">
-        <v>124096000</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>Omad Tekstil MChJ</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>382730428</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>20208000878388860001</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №9484 за поставленный товар</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>23.09.2026</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="n">
-        <v>36818000</v>
-      </c>
-      <c r="D180" s="2" t="n"/>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>НДС за август 2026 г.</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>23.09.2026</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="n">
-        <v>96956000</v>
-      </c>
-      <c r="D181" s="2" t="n"/>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Toshkent Avto Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>200251378</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>20208000751791027001</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>Оплата за сырье по договору №269/26 от 23.09.2026, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>23.09.2026</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="n">
-        <v>178066000</v>
-      </c>
-      <c r="D182" s="2" t="n"/>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>Toshkent Avto Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>200251378</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>20208000751791027001</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>Оплата за сырье по договору №270/26 от 23.09.2026, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>24.09.2026</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="n"/>
-      <c r="D183" s="2" t="n">
-        <v>224564000</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Chust Agro MChJ</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>262401919</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>20208000060416519001</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №213/26, QQS 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>24.09.2026</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="n"/>
-      <c r="D184" s="2" t="n">
-        <v>65735000</v>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>Jizzax Plastik AJ</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>261879358</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>20208000005154280001</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>Оплата по с/ф №1937 за поставленный товар</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>25.09.2026</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="n">
-        <v>13878000</v>
-      </c>
-      <c r="D185" s="2" t="n"/>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>200933985</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>20208000442705419001</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>Оплата за электроэнергию согласно счету</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="n"/>
-      <c r="D186" s="2" t="n">
-        <v>67821000</v>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>Qo'qon Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>305246474</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>20208000686433325001</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по дог. №270/26 от 28.09.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="C187" s="2" t="n">
-        <v>103652000</v>
-      </c>
-      <c r="D187" s="2" t="n"/>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>Yangi Hayot Agro MChJ</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>336608635</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>20208000726090628001</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №5733</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="C188" s="2" t="n">
-        <v>229227000</v>
-      </c>
-      <c r="D188" s="2" t="n"/>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>Toshkent Avto Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>200251378</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>20208000751791027001</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>Оплата за транспортные услуги по договору №74/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="C189" s="2" t="n"/>
-      <c r="D189" s="2" t="n">
-        <v>138212000</v>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>Qo'qon Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>305246474</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>20208000686433325001</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>Оплата за товар по счет-фактуре №4618 от 29.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="C190" s="2" t="n">
-        <v>92655000</v>
-      </c>
-      <c r="D190" s="2" t="n"/>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>Nukus Dori-Darmon XK</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>277098460</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>20208000251866498001</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №288/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="C191" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D191" s="2" t="n"/>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>Bodomzor Bank ATB</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>45994000900000001001</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>Плата за SMS-информирование</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>Jami aylanma:</t>
-        </is>
-      </c>
-      <c r="C192" s="4" t="n">
-        <v>9919852000</v>
-      </c>
-      <c r="D192" s="4" t="n">
-        <v>9877852000</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
           <t>Davr oxiridagi qoldiq:</t>
         </is>
       </c>
-      <c r="C193" s="4" t="n">
+      <c r="C157" s="4" t="n">
         <v>411600000</v>
       </c>
-      <c r="D193" s="4" t="n"/>
+      <c r="D157" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
